--- a/6.2 Geoffrey Bay/output/yearly_total_coral_cover_growth_param_0.5.xlsx
+++ b/6.2 Geoffrey Bay/output/yearly_total_coral_cover_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.236081106884247</v>
+        <v>1.300557590376095</v>
       </c>
       <c r="C3" t="n">
-        <v>4.52014049509615</v>
+        <v>4.705276627743864</v>
       </c>
       <c r="D3" t="n">
-        <v>5.943775490867378</v>
+        <v>6.142220157292103</v>
       </c>
       <c r="E3" t="n">
-        <v>11.69999709284778</v>
+        <v>12.14805437541206</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.312076354294735</v>
+        <v>1.432299391794535</v>
       </c>
       <c r="C4" t="n">
-        <v>4.763626393069331</v>
+        <v>5.131383162936911</v>
       </c>
       <c r="D4" t="n">
-        <v>5.986972389854238</v>
+        <v>6.391768109103305</v>
       </c>
       <c r="E4" t="n">
-        <v>12.0626751372183</v>
+        <v>12.95545066383475</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.45505808994124</v>
+        <v>1.621107519421364</v>
       </c>
       <c r="C5" t="n">
-        <v>5.10320310649126</v>
+        <v>5.633183927186009</v>
       </c>
       <c r="D5" t="n">
-        <v>6.021313924548792</v>
+        <v>6.628556666433314</v>
       </c>
       <c r="E5" t="n">
-        <v>12.57957512098129</v>
+        <v>13.88284811304069</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.651221098726795</v>
+        <v>1.858868305054367</v>
       </c>
       <c r="C6" t="n">
-        <v>5.542221044876348</v>
+        <v>6.229872720730001</v>
       </c>
       <c r="D6" t="n">
-        <v>6.124662505374854</v>
+        <v>6.95158776749438</v>
       </c>
       <c r="E6" t="n">
-        <v>13.318104648978</v>
+        <v>15.04032879327875</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.906338057152371</v>
+        <v>2.154010692626095</v>
       </c>
       <c r="C7" t="n">
-        <v>6.047880017425711</v>
+        <v>6.899237092422053</v>
       </c>
       <c r="D7" t="n">
-        <v>6.227795101705981</v>
+        <v>7.237764394171479</v>
       </c>
       <c r="E7" t="n">
-        <v>14.18201317628406</v>
+        <v>16.29101217921963</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.150726119101771</v>
+        <v>1.251456757879108</v>
       </c>
       <c r="C8" t="n">
-        <v>3.832605592700953</v>
+        <v>4.322050489844044</v>
       </c>
       <c r="D8" t="n">
-        <v>4.426396056660551</v>
+        <v>5.235663831069854</v>
       </c>
       <c r="E8" t="n">
-        <v>9.409727768463275</v>
+        <v>10.80917107879301</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.8826500909801375</v>
+        <v>0.9360678149050107</v>
       </c>
       <c r="C9" t="n">
-        <v>2.718773552324777</v>
+        <v>3.005443704143358</v>
       </c>
       <c r="D9" t="n">
-        <v>3.37344219142472</v>
+        <v>4.060186190696014</v>
       </c>
       <c r="E9" t="n">
-        <v>6.974865834729634</v>
+        <v>8.001697709744382</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.277204675839888</v>
+        <v>1.359513775269165</v>
       </c>
       <c r="C10" t="n">
-        <v>3.362849133695897</v>
+        <v>3.726680600242384</v>
       </c>
       <c r="D10" t="n">
-        <v>3.691312463105752</v>
+        <v>4.554726976085818</v>
       </c>
       <c r="E10" t="n">
-        <v>8.331366272641537</v>
+        <v>9.640921351597367</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.729525295617521</v>
+        <v>1.843408029310151</v>
       </c>
       <c r="C11" t="n">
-        <v>4.097638202939422</v>
+        <v>4.544482311573841</v>
       </c>
       <c r="D11" t="n">
-        <v>4.012717026522073</v>
+        <v>5.038913957407791</v>
       </c>
       <c r="E11" t="n">
-        <v>9.839880525079016</v>
+        <v>11.42680429829178</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.23318150285022</v>
+        <v>2.390948358922682</v>
       </c>
       <c r="C12" t="n">
-        <v>4.897723311992403</v>
+        <v>5.432266755649826</v>
       </c>
       <c r="D12" t="n">
-        <v>4.32332236519168</v>
+        <v>5.516044089227358</v>
       </c>
       <c r="E12" t="n">
-        <v>11.4542271800343</v>
+        <v>13.33925920379987</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.805609136765407</v>
+        <v>3.003745458436499</v>
       </c>
       <c r="C13" t="n">
-        <v>5.739503246044745</v>
+        <v>6.358317504278951</v>
       </c>
       <c r="D13" t="n">
-        <v>4.676702451335319</v>
+        <v>6.060995808049589</v>
       </c>
       <c r="E13" t="n">
-        <v>13.22181483414547</v>
+        <v>15.42305877076504</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.680702982285327</v>
+        <v>1.790825622270692</v>
       </c>
       <c r="C14" t="n">
-        <v>4.005128116768245</v>
+        <v>4.400752806625625</v>
       </c>
       <c r="D14" t="n">
-        <v>3.538817592205096</v>
+        <v>4.655938487390498</v>
       </c>
       <c r="E14" t="n">
-        <v>9.224648691258668</v>
+        <v>10.84751691628681</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.983091092670387</v>
+        <v>2.084319098455276</v>
       </c>
       <c r="C15" t="n">
-        <v>4.437146194022055</v>
+        <v>4.826507333526339</v>
       </c>
       <c r="D15" t="n">
-        <v>3.677489455429957</v>
+        <v>4.84401189509306</v>
       </c>
       <c r="E15" t="n">
-        <v>10.0977267421224</v>
+        <v>11.75483832707468</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.560594362216531</v>
+        <v>2.680505026813236</v>
       </c>
       <c r="C16" t="n">
-        <v>5.324390864258066</v>
+        <v>5.758077912609095</v>
       </c>
       <c r="D16" t="n">
-        <v>3.999610694670378</v>
+        <v>5.310970373141013</v>
       </c>
       <c r="E16" t="n">
-        <v>11.88459592114497</v>
+        <v>13.74955331256334</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.214420304222063</v>
+        <v>2.301000634259589</v>
       </c>
       <c r="C17" t="n">
-        <v>4.946506355416427</v>
+        <v>5.345095923340632</v>
       </c>
       <c r="D17" t="n">
-        <v>3.785795862162465</v>
+        <v>5.046075207581139</v>
       </c>
       <c r="E17" t="n">
-        <v>10.94672252180096</v>
+        <v>12.69217176518136</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.767664587996268</v>
+        <v>2.865574286540803</v>
       </c>
       <c r="C18" t="n">
-        <v>5.843705947373502</v>
+        <v>6.274879721601659</v>
       </c>
       <c r="D18" t="n">
-        <v>4.095684525007972</v>
+        <v>5.497227547590717</v>
       </c>
       <c r="E18" t="n">
-        <v>12.70705506037774</v>
+        <v>14.63768155573318</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>3.012610640205847</v>
+        <v>3.102234388126539</v>
       </c>
       <c r="C19" t="n">
-        <v>6.311086576934281</v>
+        <v>6.759411483555629</v>
       </c>
       <c r="D19" t="n">
-        <v>4.233443362867883</v>
+        <v>5.707468818455172</v>
       </c>
       <c r="E19" t="n">
-        <v>13.55714058000801</v>
+        <v>15.56911469013734</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>3.614284538230548</v>
+        <v>3.715227837181205</v>
       </c>
       <c r="C20" t="n">
-        <v>7.268457485684643</v>
+        <v>7.796353043735195</v>
       </c>
       <c r="D20" t="n">
-        <v>4.520967813010647</v>
+        <v>6.157992839934034</v>
       </c>
       <c r="E20" t="n">
-        <v>15.40370983692584</v>
+        <v>17.66957372085043</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>2.30923749749822</v>
+        <v>2.370204029931947</v>
       </c>
       <c r="C21" t="n">
-        <v>5.267096068238224</v>
+        <v>5.696757951001841</v>
       </c>
       <c r="D21" t="n">
-        <v>3.758149846810875</v>
+        <v>5.171954898219664</v>
       </c>
       <c r="E21" t="n">
-        <v>11.33448341254732</v>
+        <v>13.23891687915345</v>
       </c>
     </row>
   </sheetData>
